--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T15:11:15+00:00</t>
+    <t>2026-09-14T07:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:29:46+00:00</t>
+    <t>2026-09-14T08:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:03:24+00:00</t>
+    <t>2026-09-14T11:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:48:09+00:00</t>
+    <t>2026-09-14T12:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:20:33+00:00</t>
+    <t>2026-09-14T12:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:53:39+00:00</t>
+    <t>2026-09-14T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/CodeSystem-mii-cs-mtb-empfehlung-status-begruendung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:42:50+00:00</t>
+    <t>2026-09-14T17:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
